--- a/docs/downloads/04/tbl_raison_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_raison_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Mariage</t>
         </is>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,14 +480,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -601,14 +589,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>7.3</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -624,14 +606,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D12">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>72.40000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +629,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scolarisation</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E13">
-        <v>0.8</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -716,14 +698,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>24</v>
-      </c>
-      <c r="E16">
-        <v>30</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -739,14 +715,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D17">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>58.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -762,14 +738,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scolarisation</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E18">
-        <v>1.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="19">
@@ -788,12 +764,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -831,14 +801,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Insécurité</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0.7</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -857,12 +821,6 @@
           <t>Mariage</t>
         </is>
       </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -900,14 +858,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E24">
-        <v>0.7</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="25">
@@ -923,14 +881,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D25">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>21.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +899,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>7.3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -969,14 +927,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D27">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -992,14 +950,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D28">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E28">
-        <v>56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1015,37 +973,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>20</v>
-      </c>
-      <c r="E29">
-        <v>20</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>3</v>
+          <t>Mariage</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1061,14 +1007,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="E31">
-        <v>2.6</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1084,14 +1030,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D32">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>78.40000000000001</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="33">
@@ -1107,14 +1053,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>11.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="34">
@@ -1125,19 +1071,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>7.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="35">
@@ -1153,14 +1099,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E35">
-        <v>17.6</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1176,14 +1122,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D36">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>65.90000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1199,37 +1145,31 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38">
-        <v>5.5</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1245,14 +1185,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Insécurité</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E39">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="40">
@@ -1268,14 +1208,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D40">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="E40">
-        <v>3.7</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1291,14 +1231,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D41">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="E41">
-        <v>71.90000000000001</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="42">
@@ -1314,14 +1254,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scolarisation</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="E42">
-        <v>0.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1332,19 +1272,13 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>0.2</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1355,19 +1289,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D44">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E44">
-        <v>15.6</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="45">
@@ -1378,19 +1312,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D45">
-        <v>43</v>
+        <v>234</v>
       </c>
       <c r="E45">
-        <v>8.300000000000001</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="46">
@@ -1406,14 +1340,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Autre</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E46">
-        <v>0.3</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1429,105 +1363,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D47">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="E47">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>234</v>
-      </c>
-      <c r="E48">
-        <v>62.2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Scolarisation</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>37</v>
-      </c>
-      <c r="E50">
-        <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>21</v>
-      </c>
-      <c r="E51">
         <v>5.6</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_raison_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_raison_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,8 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>117</v>
+      </c>
+      <c r="E2">
+        <v>81.8</v>
       </c>
     </row>
     <row r="3">
@@ -411,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>69.90000000000001</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="4">
@@ -429,19 +435,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>18.2</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -452,19 +452,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>9.1</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="6">
@@ -480,83 +480,83 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Autre raison</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>20</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D8">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E8">
-        <v>67.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -566,14 +566,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10">
-        <v>6.7</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -584,13 +578,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Autre raison</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>77</v>
+      </c>
+      <c r="E11">
+        <v>96.2</v>
       </c>
     </row>
     <row r="12">
@@ -601,25 +601,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12">
-        <v>7.3</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -629,20 +623,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>89</v>
-      </c>
-      <c r="E13">
-        <v>72.40000000000001</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -652,20 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
-      <c r="E14">
-        <v>10.6</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -675,37 +657,43 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E15">
-        <v>8.9</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Autre raison</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>29</v>
+      </c>
+      <c r="E16">
+        <v>21.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -715,20 +703,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D17">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -738,94 +726,112 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D18">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>58.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>103</v>
+      </c>
+      <c r="E19">
+        <v>88.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E20">
-        <v>7.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Autre raison</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>81</v>
+      </c>
+      <c r="E21">
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22">
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -835,20 +841,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>93</v>
-      </c>
-      <c r="E23">
-        <v>67.90000000000001</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -858,20 +858,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>29</v>
-      </c>
-      <c r="E24">
-        <v>21.2</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -881,43 +875,43 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>435</v>
       </c>
       <c r="E25">
-        <v>7.3</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D26">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="E26">
-        <v>21</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -927,20 +921,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>56</v>
-      </c>
-      <c r="E27">
-        <v>56</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -950,20 +938,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>20</v>
-      </c>
-      <c r="E28">
-        <v>20</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -973,404 +955,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>337</v>
+      </c>
+      <c r="E29">
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>91</v>
-      </c>
-      <c r="E31">
-        <v>78.40000000000001</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>13</v>
-      </c>
-      <c r="E32">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>9</v>
-      </c>
-      <c r="E33">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>16</v>
-      </c>
-      <c r="E34">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>60</v>
-      </c>
-      <c r="E35">
-        <v>65.90000000000001</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>10</v>
-      </c>
-      <c r="E36">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Marovoay - Maroala</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>5</v>
-      </c>
-      <c r="E37">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>19</v>
-      </c>
-      <c r="E39">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>373</v>
-      </c>
-      <c r="E40">
-        <v>71.90000000000001</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>81</v>
-      </c>
-      <c r="E41">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>43</v>
-      </c>
-      <c r="E42">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>82</v>
-      </c>
-      <c r="E44">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>234</v>
-      </c>
-      <c r="E45">
-        <v>62.2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D46">
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D30">
         <v>37</v>
       </c>
-      <c r="E46">
+      <c r="E30">
         <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>21</v>
-      </c>
-      <c r="E47">
-        <v>5.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_raison_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_raison_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -808,7 +808,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
